--- a/agent_runs/manjidiwang/episodes/ep18/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep18/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>五亿资金集结（，总时长：10秒，镜头数：4个）</t>
+          <t>五亿资金集结</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>权限冻结爆出（，总时长：10秒，镜头数：4个）</t>
+          <t>权限冻结爆出</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>账户锁死对峙（，总时长：11秒，镜头数：5个）</t>
+          <t>账户锁死对峙</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>账本砸穿谎言（，总时长：11秒，镜头数：5个）</t>
+          <t>账本砸穿谎言</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>五亿债务雷爆出（，总时长：10秒，镜头数：4个）</t>
+          <t>五亿债务雷爆出</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>政策公告反转（，总时长：12秒，镜头数：5个）</t>
+          <t>政策公告反转</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>赚了钱也坐牢（，总时长：12秒，镜头数：5个）</t>
+          <t>赚了钱也坐牢</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>警车前的龙爷线索（，总时长：14秒，镜头数：5个）</t>
+          <t>警车前的龙爷线索</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>更大的棋局浮现（，总时长：10秒，镜头数：5个）</t>
+          <t>更大的棋局浮现</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
